--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.16313792405241</v>
+        <v>10.75150991265852</v>
       </c>
       <c r="D2" t="n">
-        <v>66.12965255528114</v>
+        <v>10.74606854023319</v>
       </c>
       <c r="E2" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F2" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.95512503256322</v>
+        <v>4.380207817791523</v>
       </c>
       <c r="D3" t="n">
-        <v>27.00596910759341</v>
+        <v>4.388469979983929</v>
       </c>
       <c r="E3" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F3" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.95428744285164</v>
+        <v>9.905071709463392</v>
       </c>
       <c r="D4" t="n">
-        <v>60.90441770600684</v>
+        <v>9.896967877226112</v>
       </c>
       <c r="E4" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F4" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.3561947078555</v>
+        <v>9.645381640026519</v>
       </c>
       <c r="D5" t="n">
-        <v>59.34374833685774</v>
+        <v>9.643359104739384</v>
       </c>
       <c r="E5" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F5" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.98018038856249</v>
+        <v>7.959279313141405</v>
       </c>
       <c r="D6" t="n">
-        <v>48.95882332134529</v>
+        <v>7.955808789718611</v>
       </c>
       <c r="E6" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F6" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.90343500301703</v>
+        <v>1.934308187990267</v>
       </c>
       <c r="D7" t="n">
-        <v>11.93178204982195</v>
+        <v>1.938914583096067</v>
       </c>
       <c r="E7" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F7" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.581438870922433</v>
+        <v>1.556983816524895</v>
       </c>
       <c r="D8" t="n">
-        <v>9.560993407514927</v>
+        <v>1.553661428721176</v>
       </c>
       <c r="E8" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F8" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.90757397498439</v>
+        <v>5.347480770934965</v>
       </c>
       <c r="D9" t="n">
-        <v>32.86100837920245</v>
+        <v>5.339913861620397</v>
       </c>
       <c r="E9" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F9" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.092805999864223</v>
+        <v>0.5025809749779362</v>
       </c>
       <c r="D10" t="n">
-        <v>3.100757080843163</v>
+        <v>0.503873025637014</v>
       </c>
       <c r="E10" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F10" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.14064585474003</v>
+        <v>6.360354951395255</v>
       </c>
       <c r="D11" t="n">
-        <v>39.08601325682393</v>
+        <v>6.351477154233888</v>
       </c>
       <c r="E11" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F11" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.6722368589263</v>
+        <v>4.984238489575524</v>
       </c>
       <c r="D12" t="n">
-        <v>30.62001925028626</v>
+        <v>4.975753128171518</v>
       </c>
       <c r="E12" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F12" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.3268100400467</v>
+        <v>3.953106631507588</v>
       </c>
       <c r="D13" t="n">
-        <v>24.4854000514246</v>
+        <v>3.978877508356498</v>
       </c>
       <c r="E13" t="n">
-        <v>20.09764281783519</v>
+        <v>3.265866957898218</v>
       </c>
       <c r="F13" t="n">
-        <v>20.07551022103156</v>
+        <v>3.262270410917628</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
